--- a/docs/mock/スプレッドシート型_gooner5_db.xlsx
+++ b/docs/mock/スプレッドシート型_gooner5_db.xlsx
@@ -430,49 +430,49 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>member_id</t>
+          <t>メンバーID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>氏名</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>所属</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>権限</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_salary</t>
+          <t>基本給</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>在籍</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>メールアドレス</t>
         </is>
       </c>
     </row>
@@ -489,12 +489,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HQ</t>
+          <t>本部</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>本部管理者</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>統括</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -551,12 +551,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>統括</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -580,12 +580,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>統括</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEMBER</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -640,36 +640,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>計画ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>year_month</t>
+          <t>対象年月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>事業部</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>target_sales</t>
+          <t>目標売上</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>target_op</t>
+          <t>目標営業利益</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>イベント営業</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>運送</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1515,25 +1515,25 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>config_key</t>
+          <t>設定キー</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>config_value</t>
+          <t>設定値</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>説明</t>
         </is>
       </c>
     </row>
@@ -2002,102 +2002,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>tx_id</t>
+          <t>伝票ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>year_month</t>
+          <t>計上年月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>計上日</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>事業部</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>member_id</t>
+          <t>担当者ID</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>案件内容</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>gross_sales</t>
+          <t>売上金額</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>direct_cost</t>
+          <t>直接経費</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>lead_source</t>
+          <t>流入経路</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>登録者ID</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>登録日時</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>承認者ID</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>approved_at</t>
+          <t>承認日時</t>
         </is>
       </c>
     </row>
@@ -2116,42 +2116,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>exp_id</t>
+          <t>経費ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>year_month</t>
+          <t>対象年月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>事業部</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>科目</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>金額</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>摘要</t>
         </is>
       </c>
     </row>
@@ -2170,54 +2170,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>送客ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>year_month</t>
+          <t>対象年月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>from_member_id</t>
+          <t>紹介元担当者ID</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>to_dept</t>
+          <t>送客先</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>client_name</t>
+          <t>案件名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>gross_amount</t>
+          <t>成立総売上</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>split_rate</t>
+          <t>紹介元配分率</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ステータス</t>
         </is>
       </c>
     </row>
